--- a/TASK2/Scenariji/SC02_KupovinaClanarine.xlsx
+++ b/TASK2/Scenariji/SC02_KupovinaClanarine.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Kupovina clanarine</t>
+          <t>Kupovina članarine</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Clan bira tip clanarine i vrsi kupovinu putem sistema. Sistem evidentira placanje i aktivira clanarinu.</t>
+          <t>Član bira tip članarine i vrsi kupovinu putem sistema. Sistem evidentira plaćanje i aktivira članarinu.</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Podrska za tri tipa clanarina (mjesecna, kvartalna, godisnja); Automatsko racunanje datuma isteka clanarine</t>
+          <t>Podrska za tri tipa članarina (mjesecna, kvartalna, godisnja); Automatsko racunanje datuma isteka članarine</t>
         </is>
       </c>
     </row>
@@ -497,31 +497,31 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Clan je prijavljen na sistem. Clan je registrovan u sistemu.</t>
+          <t>Član je prijavljen na sistem. Član je registrovan u sistemu.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - uspjesan zavrsetak</t>
+          <t>Posljedice - uspješan završetak</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Clanarina je aktivirana, datum isteka je izracunat, placanje je evidentirano.</t>
+          <t>Članarina je aktivirana, datum isteka je izračunat, plaćanje je evidentirano.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - neuspjesan zavrsetak</t>
+          <t>Posljedice - neuspješan završetak</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Kupovina nije izvrsena, clan nema aktivnu clanarinu.</t>
+          <t>Kupovina nije izvršena, član nema aktivnu članarinu.</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Clan bira tip clanarine, sistem evidentira placanje i aktivira clanarinu.</t>
+          <t>Član bira tip članarine, sistem evidentira plaćanje i aktivira članarinu.</t>
         </is>
       </c>
     </row>
@@ -569,10 +569,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Clan vec ima aktivnu clanarinu, Odustajanje od kupovine</t>
-        </is>
-      </c>
-    </row>
+          <t>Član već ima aktivnu članarinu, Odustajanje od kupovine</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -583,7 +584,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -595,28 +596,28 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1. Pokretanje opcije za kupovinu clanarine</t>
+          <t>1. Pokretanje opcije za kupovinu članarine</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2. Prikaz dostupnih tipova clanarina sa cijenama</t>
+          <t>2. Prikaz dostupnih tipova članarina sa cijenama</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>3. Odabir tipa clanarine (mjesecna, kvartalna, godisnja)</t>
+          <t>3. Odabir tipa članarine (mjesecna, kvartalna, godisnja)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>4. Prikaz detalja odabrane clanarine i ukupne cijene</t>
+          <t>4. Prikaz detalja odabrane članarine i ukupne cijene</t>
         </is>
       </c>
     </row>
@@ -630,14 +631,14 @@
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>6. Evidentiranje placanja</t>
+          <t>6. Evidentiranje plaćanja</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>7. Aktiviranje clanarine i izracun datuma isteka</t>
+          <t>7. Aktiviranje članarine i Izračun datuma isteka</t>
         </is>
       </c>
     </row>
@@ -648,17 +649,18 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Alternativni Tok - Clan vec ima aktivnu clanarinu</t>
+          <t>Alternativni Tok - Član već ima aktivnu članarinu</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -670,7 +672,7 @@
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1a. Sistem detektuje da clan vec ima aktivnu clanarinu</t>
+          <t>1a. Sistem detektuje da član već ima aktivnu članarinu</t>
         </is>
       </c>
     </row>
@@ -684,14 +686,14 @@
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1c. Ponuda opcije produzenja clanarine</t>
+          <t>1c. Ponuda opcije produženja članarine</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1d. Clan bira produzenje ili odustaje</t>
+          <t>1d. Član bira produženje ili odustaje</t>
         </is>
       </c>
     </row>
